--- a/MainTop/13.03.2026 Макс ВБ/13.03.2026 Макс ВБ.xlsx
+++ b/MainTop/13.03.2026 Макс ВБ/13.03.2026 Макс ВБ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\13.03.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECC9CF15-B6FC-4DD1-8873-FAAE2065D15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1EA946-AF28-4778-9139-52230A55AC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{478D09C0-639C-4E70-9D45-D59797C0B52F}"/>
   </bookViews>
@@ -5538,17 +5538,50 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
-      <c r="F128" s="1"/>
-      <c r="G128" s="1"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
-      <c r="K128" s="1"/>
-      <c r="L128" s="1"/>
+      <c r="B128" s="1">
+        <f t="shared" ref="B128:K128" si="0">SUM(B2:B127)</f>
+        <v>425</v>
+      </c>
+      <c r="C128" s="1">
+        <f t="shared" si="0"/>
+        <v>412</v>
+      </c>
+      <c r="D128" s="1">
+        <f t="shared" si="0"/>
+        <v>394</v>
+      </c>
+      <c r="E128" s="1">
+        <f t="shared" si="0"/>
+        <v>383</v>
+      </c>
+      <c r="F128" s="1">
+        <f t="shared" si="0"/>
+        <v>371</v>
+      </c>
+      <c r="G128" s="1">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+      <c r="H128" s="1">
+        <f t="shared" si="0"/>
+        <v>348</v>
+      </c>
+      <c r="I128" s="1">
+        <f t="shared" si="0"/>
+        <v>336</v>
+      </c>
+      <c r="J128" s="1">
+        <f t="shared" si="0"/>
+        <v>330</v>
+      </c>
+      <c r="K128" s="1">
+        <f t="shared" si="0"/>
+        <v>321</v>
+      </c>
+      <c r="L128" s="1">
+        <f>SUM(L2:L127)</f>
+        <v>311</v>
+      </c>
       <c r="M128" s="1"/>
       <c r="N128" s="1"/>
     </row>
